--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10539,14 +10539,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2C · Top 100 corp · ordenado por CR únicos ↓</t>
+          <t>B2C · Top 100 corp · ordenado por Eficacia ↑ (menor a mayor)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10608,32 +10608,32 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Melia</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, HBSI, Internal</t>
+          <t>HBSI, Internal</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>96233</v>
+        <v>208</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>89568</v>
+        <v>19</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.9307410139972775</v>
+        <v>0.09134615384615384</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.0002493946982843723</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.004807692307692308</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -10648,32 +10648,32 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Krystal</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>66827</v>
+        <v>568</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>62855</v>
+        <v>59</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.9405629461145945</v>
+        <v>0.1038732394366197</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>0.001092372843311835</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.00352112676056338</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -10688,37 +10688,37 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Alsol</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>Internal, Siteminder</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>50589</v>
+        <v>186</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>49518</v>
+        <v>53</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.9788293897882939</v>
+        <v>0.2849462365591398</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.0003558085749866572</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -10728,28 +10728,28 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, HBSI, Internal, Siteminder, SynXis, Travelclick</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>33503</v>
+        <v>12391</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>25820</v>
+        <v>8723</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>630</v>
+        <v>29</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.7706772527833329</v>
+        <v>0.7039786942135421</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>0.01880428618332687</v>
+        <v>0.00234040836090711</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -10768,37 +10768,37 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Accor</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, Internal, SynXis</t>
+          <t>DerbySoft, HBSI, Internal, Siteminder, SynXis, Travelclick</t>
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>18457</v>
+        <v>33503</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>17138</v>
+        <v>25820</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>30</v>
+        <v>630</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.9285365985804843</v>
+        <v>0.7706772527833329</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.00162539957739611</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.01880428618332687</v>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -10808,37 +10808,37 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Presidente Intercontinental</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>12391</v>
+        <v>1452</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>8723</v>
+        <v>1250</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.7039786942135421</v>
+        <v>0.8608815426997245</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>0.00234040836090711</v>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>0</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -10848,28 +10848,28 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Wyndham</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Internal</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>12092</v>
+        <v>1993</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>11013</v>
+        <v>1739</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.9107674495534237</v>
+        <v>0.8725539387857502</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.001984783327820046</v>
+        <v>0.003010536879076769</v>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
@@ -10888,32 +10888,32 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>Wyndham</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>DerbySoft, Internal</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>10318</v>
+        <v>12092</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>10302</v>
+        <v>11013</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.9984493118821477</v>
+        <v>0.9107674495534237</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0.001163016088389223</v>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.001984783327820046</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -10928,37 +10928,37 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>Velas Resorts</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>5003</v>
+        <v>75</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>4997</v>
+        <v>69</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.998800719568259</v>
+        <v>0.92</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.00779532280631621</v>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -10968,32 +10968,32 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Best Western</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, SynXis</t>
+          <t>SynXis</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>3456</v>
+        <v>1733</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3333</v>
+        <v>1598</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.9644097222222222</v>
+        <v>0.9221004039238315</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>0.0005787037037037037</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.001731102135025967</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -11008,32 +11008,32 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>MGM Resorts</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>DerbySoft, Expedia, Internal, SynXis</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>3396</v>
+        <v>18457</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>3280</v>
+        <v>17138</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.9658421672555948</v>
+        <v>0.9285365985804843</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.00176678445229682</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.00162539957739611</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -11048,32 +11048,32 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Universal</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>DerbySoft, HBSI, Internal</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>1993</v>
+        <v>96233</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>1739</v>
+        <v>89568</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.8725539387857502</v>
+        <v>0.9307410139972775</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>0.003010536879076769</v>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.0002493946982843723</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -11088,37 +11088,37 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>Hoteles Geh Suites</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>1733</v>
+        <v>809</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>1598</v>
+        <v>759</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.9221004039238315</v>
+        <v>0.9381953028430161</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.001731102135025967</v>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
+        <v>0.01359703337453646</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -11128,37 +11128,37 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>CHOICE</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Internal</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>1528</v>
+        <v>66827</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>1510</v>
+        <v>62855</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.9882198952879581</v>
+        <v>0.9405629461145945</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0.0137434554973822</v>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.001092372843311835</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -11168,28 +11168,28 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>PAM Hotels</t>
+          <t>Karisma</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Internal, SynXis</t>
+          <t>SynXis</t>
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>1523</v>
+        <v>451</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>1455</v>
+        <v>426</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.9553512803676953</v>
+        <v>0.9445676274944568</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.001313197636244255</v>
+        <v>0.002217294900221729</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -11208,37 +11208,37 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Presidente Intercontinental</t>
+          <t>PAM Hotels</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>Internal, SynXis</t>
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>1452</v>
+        <v>1523</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>1250</v>
+        <v>1455</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.8608815426997245</v>
+        <v>0.9553512803676953</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.001313197636244255</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -11248,37 +11248,37 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Camino Real</t>
+          <t>Americas Hotels Group</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Internal, Travelclick</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1248</v>
+        <v>594</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1248</v>
+        <v>569</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>1</v>
+        <v>0.9579124579124579</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0.07932692307692307</v>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.01346801346801347</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -11288,37 +11288,37 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Wynn Las Vegas</t>
+          <t>Faranda Hotels</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>DerbySoft, Siteminder</t>
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>864</v>
+        <v>252</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>862</v>
+        <v>243</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.9976851851851852</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>0.009259259259259259</v>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.003968253968253968</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -11328,28 +11328,28 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Geh Suites</t>
+          <t>Best Western</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>DerbySoft, Expedia, SynXis</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>809</v>
+        <v>3456</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>759</v>
+        <v>3333</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.9381953028430161</v>
+        <v>0.9644097222222222</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>0.01359703337453646</v>
+        <v>0.0005787037037037037</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>GRUPO POSADAS</t>
+          <t>MGM Resorts</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -11377,23 +11377,23 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>801</v>
+        <v>3396</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>788</v>
+        <v>3280</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.9837702871410736</v>
+        <v>0.9658421672555948</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>0.001248439450686642</v>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.00176678445229682</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Sandos</t>
+          <t>Bahia Principe</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -11417,19 +11417,19 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>770</v>
+        <v>546</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>770</v>
+        <v>532</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>1</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.002597402597402597</v>
+        <v>0</v>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Decameron</t>
+          <t>GHL</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -11457,19 +11457,19 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>647</v>
+        <v>188</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>646</v>
+        <v>184</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.9984544049459042</v>
+        <v>0.9787234042553191</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>0.00463678516228748</v>
+        <v>0.01063829787234043</v>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -11488,28 +11488,28 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Park Royal</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Internal, Siteminder</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>609</v>
+        <v>50589</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>608</v>
+        <v>49518</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.9983579638752053</v>
+        <v>0.9788293897882939</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0.001642036124794745</v>
+        <v>0.0003558085749866572</v>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
@@ -11528,37 +11528,37 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Americas Hotels Group</t>
+          <t>GRUPO POSADAS</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>594</v>
+        <v>801</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>569</v>
+        <v>788</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.9579124579124579</v>
+        <v>0.9837702871410736</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>0.01346801346801347</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.001248439450686642</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Krystal</t>
+          <t>Mision</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -11577,28 +11577,28 @@
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>568</v>
+        <v>494</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>59</v>
+        <v>486</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.1038732394366197</v>
+        <v>0.9838056680161943</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.00352112676056338</v>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Súper Crítica</t>
+        <v>0.04453441295546558</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe</t>
+          <t>Oxo Hotel</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -11617,19 +11617,19 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>546</v>
+        <v>246</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>532</v>
+        <v>243</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9878048780487805</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>0</v>
+        <v>0.008130081300813009</v>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -11648,28 +11648,28 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Ocean by H10</t>
+          <t>CHOICE</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>DerbySoft, Internal</t>
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>540</v>
+        <v>1528</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>540</v>
+        <v>1510</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1</v>
+        <v>0.9882198952879581</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.003703703703703704</v>
+        <v>0.0137434554973822</v>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Movich</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -11697,19 +11697,19 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.9944237918215614</v>
+        <v>0.9886363636363636</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>0.06691449814126393</v>
+        <v>0.003787878787878788</v>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -11728,28 +11728,28 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Palace</t>
+          <t>Iberostar</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>HBSI, Internal</t>
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>532</v>
+        <v>157</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>529</v>
+        <v>156</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.9943609022556391</v>
+        <v>0.9936305732484076</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0.003759398496240601</v>
+        <v>0.05732484076433121</v>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Marriott</t>
+          <t>Palace</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -11777,19 +11777,19 @@
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.9886363636363636</v>
+        <v>0.9943609022556391</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>0.003787878787878788</v>
+        <v>0.003759398496240601</v>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Mision</t>
+          <t>Hoteles Movich</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -11817,19 +11817,19 @@
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>494</v>
+        <v>538</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>486</v>
+        <v>535</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.9838056680161943</v>
+        <v>0.9944237918215614</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0.04453441295546558</v>
+        <v>0.06691449814126393</v>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
@@ -11848,28 +11848,28 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Oasis</t>
+          <t>Emporio</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal, Siteminder</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>492</v>
+        <v>379</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>492</v>
+        <v>378</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1</v>
+        <v>0.9973614775725593</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>0</v>
+        <v>0.002638522427440633</v>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -11888,28 +11888,28 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Dann</t>
+          <t>Wynn Las Vegas</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>489</v>
+        <v>864</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>489</v>
+        <v>862</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>1</v>
+        <v>0.9976851851851852</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>0.01840490797546012</v>
+        <v>0.009259259259259259</v>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -11928,32 +11928,32 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Karisma</t>
+          <t>Park Royal</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>Internal, Siteminder</t>
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>451</v>
+        <v>609</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>426</v>
+        <v>608</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.9445676274944568</v>
+        <v>0.9983579638752053</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>0.002217294900221729</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.001642036124794745</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Xcaret</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -11977,19 +11977,19 @@
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>436</v>
+        <v>10318</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>436</v>
+        <v>10302</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1</v>
+        <v>0.9984493118821477</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0.006880733944954129</v>
+        <v>0.001163016088389223</v>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
@@ -12008,28 +12008,28 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Emporio</t>
+          <t>Decameron</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Internal, Siteminder</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>379</v>
+        <v>647</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>378</v>
+        <v>646</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.9973614775725593</v>
+        <v>0.9984544049459042</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>0.002638522427440633</v>
+        <v>0.00463678516228748</v>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
@@ -12048,28 +12048,28 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>EM Hotels</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>287</v>
+        <v>5003</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>287</v>
+        <v>4997</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>1</v>
+        <v>0.998800719568259</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>0.01045296167247387</v>
+        <v>0.00779532280631621</v>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12088,32 +12088,32 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Faranda Hotels</t>
+          <t>Ocean by H10</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Siteminder</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>252</v>
+        <v>540</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>243</v>
+        <v>540</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.9642857142857143</v>
+        <v>1</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>0.003968253968253968</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.003703703703703704</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -12128,28 +12128,28 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Oxo Hotel</t>
+          <t>Camino Real</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal, Travelclick</t>
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>246</v>
+        <v>1248</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>243</v>
+        <v>1248</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.9878048780487805</v>
+        <v>1</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0.008130081300813009</v>
+        <v>0.07932692307692307</v>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>BH Hoteles</t>
+          <t>Sandos</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -12177,19 +12177,19 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>234</v>
+        <v>770</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>234</v>
+        <v>770</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G45" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>0.04273504273504274</v>
+        <v>0.002597402597402597</v>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12208,28 +12208,28 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Dorado Plaza</t>
+          <t>Oasis</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>211</v>
+        <v>492</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>211</v>
+        <v>492</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>0.004739336492890996</v>
+        <v>0</v>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -12248,37 +12248,37 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Melia</t>
+          <t>BH Hoteles</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>HBSI, Internal</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>19</v>
+        <v>234</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.09134615384615384</v>
+        <v>1</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>0.004807692307692308</v>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>Súper Crítica</t>
+        <v>0.04273504273504274</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -12288,28 +12288,28 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Palladium Hotel Group</t>
+          <t>Dann</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>204</v>
+        <v>489</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>204</v>
+        <v>489</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G48" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>0.02450980392156863</v>
+        <v>0.01840490797546012</v>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
@@ -12328,28 +12328,28 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>GHL</t>
+          <t>EM Hotels</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Siteminder</t>
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>188</v>
+        <v>287</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>184</v>
+        <v>287</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.9787234042553191</v>
+        <v>1</v>
       </c>
       <c r="H49" s="13" t="n">
-        <v>0.01063829787234043</v>
+        <v>0.01045296167247387</v>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
@@ -12368,37 +12368,37 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Alsol</t>
+          <t>Palladium Hotel Group</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Internal, Siteminder</t>
+          <t>Siteminder</t>
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>53</v>
+        <v>204</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.2849462365591398</v>
+        <v>1</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>Súper Crítica</t>
+        <v>0.02450980392156863</v>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -12408,28 +12408,28 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Iberostar</t>
+          <t>Dorado Plaza</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>HBSI, Internal</t>
+          <t>Siteminder</t>
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>156</v>
+        <v>211</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.9936305732484076</v>
+        <v>1</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>0.05732484076433121</v>
+        <v>0.004739336492890996</v>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12488,7 +12488,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Lomas Hospitality</t>
+          <t>Hoteles Xcaret</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -12497,19 +12497,19 @@
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>109</v>
+        <v>436</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>109</v>
+        <v>436</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>0</v>
+        <v>0.006880733944954129</v>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>RIU</t>
+          <t>Lomas Hospitality</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -12537,10 +12537,10 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>0</v>
@@ -12568,32 +12568,32 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Velas Resorts</t>
+          <t>RIU</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="H55" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4615,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14185,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4615,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14185,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
